--- a/output/pdf_financials_xlsx/FLT.xlsx
+++ b/output/pdf_financials_xlsx/FLT.xlsx
@@ -2804,13 +2804,13 @@
         <v>0.34359</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0</v>
+        <v>2.022836</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.368715</v>
+        <v>2.564898</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>42.900333</v>
+        <v>1.756129</v>
       </c>
     </row>
     <row r="49">
@@ -5035,34 +5035,34 @@
         <v>1.923173</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.923173</v>
+        <v>0.036127</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.056586</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.715365</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.744453</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>13.627437</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>10.518174</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.685302</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.211831</v>
+        <v>8.832329</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.211831</v>
+        <v>10.192756</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.211831</v>
+        <v>16.110605</v>
       </c>
     </row>
     <row r="93">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9690,7 +9690,11 @@
           <t>Warrants reserve 16</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -9774,7 +9778,11 @@
           <t>Share-based payment reserve 16</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11408,7 +11416,11 @@
           <t>Warrants reserve 17</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -11492,7 +11504,11 @@
           <t>Share-based payment reserve 17</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -13332,7 +13348,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FLT.xlsx
+++ b/output/pdf_financials_xlsx/FLT.xlsx
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003451</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004476</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006638</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.017521</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.007003</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -978,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.061842</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.297345</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.404976</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1697,19 +1697,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>6.28865</v>
+        <v>7.436599</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>9.98916</v>
+        <v>11.00897</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>15.8181</v>
+        <v>15.907584</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>24.46915</v>
+        <v>22.938891</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>45.14644</v>
+        <v>24.060896</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>73.095125</v>
@@ -1748,19 +1748,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.125773</v>
+        <v>-0.129224</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.499458</v>
+        <v>-0.503934</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.790905</v>
+        <v>-0.797543</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.489383</v>
+        <v>-0.506904</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.257322</v>
+        <v>-2.264325</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.923805</v>
@@ -1775,13 +1775,13 @@
         <v>-15.597204</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-14.699679</v>
+        <v>-14.637837</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-13.414231</v>
+        <v>-13.116886</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-19.686188</v>
+        <v>-19.281212</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-26.687634</v>
@@ -1846,19 +1846,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.125773</v>
+        <v>-0.129224</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.499458</v>
+        <v>-0.503934</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.790905</v>
+        <v>-0.797543</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.489383</v>
+        <v>-0.506904</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.257322</v>
+        <v>-2.264325</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.923805</v>
@@ -1873,13 +1873,13 @@
         <v>-15.597204</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-13.843338</v>
+        <v>-13.781496</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-12.407649</v>
+        <v>-12.110304</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-15.652457</v>
+        <v>-15.247481</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-21.862954</v>
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-4132.056008094967</v>
+        <v>-4113.596976923972</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1501.326039450853</v>
+        <v>-1465.347282218076</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-44.88440924542513</v>
+        <v>-43.72311498225767</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-80.53420484175767</v>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.432902</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.304494</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.263853</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.120993</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.393905</v>
@@ -2118,13 +2118,13 @@
         <v>15.298794</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>7.379807</v>
+        <v>1.256743</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.558909</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>41.114832</v>
       </c>
     </row>
     <row r="35">
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.028451</v>
+        <v>1.461353</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.526765</v>
+        <v>0.831259</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.533202</v>
+        <v>1.797055</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.728792</v>
+        <v>0.849785</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.879006</v>
@@ -2216,13 +2216,13 @@
         <v>15.298794</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>7.379807</v>
+        <v>1.256743</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.558909</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>41.114832</v>
       </c>
     </row>
     <row r="37">
@@ -2771,16 +2771,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.433</v>
+        <v>9.8e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.635846</v>
+        <v>0.331352</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.303324</v>
+        <v>0.039471</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.139157</v>
+        <v>0.018164</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -2804,13 +2804,13 @@
         <v>0.34359</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.022836</v>
+        <v>2.448495</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.564898</v>
+        <v>2.809806</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.756129</v>
+        <v>1.785501</v>
       </c>
     </row>
     <row r="49">
@@ -6584,13 +6584,13 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.226052</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.256341</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.22282</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -6633,13 +6633,13 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.226052</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.256341</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.22282</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -23606,7 +23606,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -36612,7 +36616,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -37982,7 +37986,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -42198,7 +42202,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" s="5" t="n">
@@ -42620,7 +42624,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E418" s="5" t="n">
@@ -43040,7 +43044,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -43392,7 +43396,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -43562,7 +43566,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">

--- a/output/pdf_financials_xlsx/FLT.xlsx
+++ b/output/pdf_financials_xlsx/FLT.xlsx
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.025026</v>
       </c>
     </row>
     <row r="113">
@@ -18844,7 +18844,11 @@
           <t>Proceeds on disposal of property, plant &amp; equipment</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -18930,7 +18934,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -21498,7 +21506,11 @@
           <t>Net Addition to Intangible assets</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FLT.xlsx
+++ b/output/pdf_financials_xlsx/FLT.xlsx
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>3.100381</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.021748</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>1.669897</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3.100381</v>
+        <v>6.200762</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.42133</v>
@@ -2461,7 +2461,7 @@
         <v>0.486664</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>3.815478</v>
+        <v>3.837226</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>4.502679</v>
@@ -2795,7 +2795,7 @@
         <v>0.214442</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.20259</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.505888</v>
@@ -2804,7 +2804,7 @@
         <v>0.34359</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.448495</v>
+        <v>2.426747</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>2.809806</v>
@@ -3635,10 +3635,10 @@
         <v>0.594903</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>3.822972</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>1.432276</v>
       </c>
     </row>
     <row r="65">
@@ -3831,10 +3831,10 @@
         <v>5.019387</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>6.331383</v>
+        <v>10.154355</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>3.433728</v>
+        <v>4.866004</v>
       </c>
     </row>
     <row r="69">
@@ -4174,10 +4174,10 @@
         <v>9.466279</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>13.412566</v>
+        <v>9.589594</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>9.540805000000001</v>
+        <v>8.108529000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5727,10 +5727,10 @@
         <v>0.08791</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.149974</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.06425</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.07328800000000001</v>
@@ -5935,25 +5935,25 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035715</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004612</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.057792</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-2.088085</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.489015</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.149379</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019598</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>-1.376636</v>
@@ -7100,25 +7100,25 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035715</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004612</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.057792</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-2.088085</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.489015</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.149379</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019598</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>-1.376636</v>
@@ -7151,25 +7151,25 @@
         <v>-0.163826</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.170603</v>
+        <v>0.134888</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-7.15411</v>
+        <v>-7.158722</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-10.630399</v>
+        <v>-10.688191</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-13.706401</v>
+        <v>-15.794486</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-11.886681</v>
+        <v>-12.375696</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-11.943111</v>
+        <v>-12.09249</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.077137</v>
+        <v>-2.096735</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-13.811481</v>
@@ -18672,7 +18672,11 @@
           <t>Cash generated from (used in) Operating Activities</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23370,7 +23374,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -29122,7 +29130,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>0.08791</v>
       </c>
